--- a/artfynd/A 15956-2022 artfynd.xlsx
+++ b/artfynd/A 15956-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15956-2022 artfynd.xlsx
+++ b/artfynd/A 15956-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1157452</v>
+        <v>536059</v>
       </c>
       <c r="B2" t="n">
-        <v>90644</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>2058</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634163.6424404341</v>
+        <v>634096</v>
       </c>
       <c r="R2" t="n">
-        <v>6633965.907861808</v>
+        <v>6634054</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-08-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-08-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrskog med lövinslag</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,37 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1157737</v>
+        <v>536060</v>
       </c>
       <c r="B3" t="n">
-        <v>90644</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>2058</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>634167.4891503395</v>
+        <v>634134</v>
       </c>
       <c r="R3" t="n">
-        <v>6633971.080187751</v>
+        <v>6634025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-09-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2009-09-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +861,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrskog med lövinslag</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1323451</v>
+        <v>1157452</v>
       </c>
       <c r="B4" t="n">
-        <v>90336</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4786</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mandelriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius volemus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634200.6549527828</v>
+        <v>634164</v>
       </c>
       <c r="R4" t="n">
-        <v>6633960.198320098</v>
+        <v>6633966</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2009-09-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-08-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2009-09-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-08-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1652026</v>
+        <v>1157737</v>
       </c>
       <c r="B5" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>634181.3570519667</v>
+        <v>634167</v>
       </c>
       <c r="R5" t="n">
-        <v>6633964.031122324</v>
+        <v>6633971</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2009-09-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2009-09-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>536060</v>
+        <v>1323451</v>
       </c>
       <c r="B6" t="n">
-        <v>90660</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2058</v>
+        <v>4786</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Mandelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Lactifluus volemus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Kuntze</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>634133.7693376396</v>
+        <v>634201</v>
       </c>
       <c r="R6" t="n">
-        <v>6634025.228829745</v>
+        <v>6633960</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,22 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2009-09-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2009-09-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,7 +1167,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Barrskog med lövinslag</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1257,6 +1182,108 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1668744</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fredriksberg, 4 km VSV Vänge, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>634090</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6633997</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hagby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2009-09-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrskog med lövinslag</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
